--- a/base_despesas/2023/despesas_202312.xlsx
+++ b/base_despesas/2023/despesas_202312.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2066 - Instalação de Playground - Francesco Tessarin 171/ 238</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2068 - Jardim de Chuva e Vagas Verdes - ao longo da R. Corinto - Jardim Rizzo, 05508-000</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -21204,7 +21204,7 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -21470,7 +21470,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -21736,7 +21736,7 @@
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -21869,7 +21869,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -22135,7 +22135,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -22268,7 +22268,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -22401,7 +22401,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -22667,7 +22667,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -22933,7 +22933,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -23066,7 +23066,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -23199,7 +23199,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -23332,7 +23332,7 @@
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -23598,7 +23598,7 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -23731,7 +23731,7 @@
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -23864,7 +23864,7 @@
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -24130,7 +24130,7 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -24263,7 +24263,7 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -24396,7 +24396,7 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -24529,7 +24529,7 @@
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -24928,7 +24928,7 @@
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -25061,7 +25061,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -25194,7 +25194,7 @@
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -25327,7 +25327,7 @@
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -25460,7 +25460,7 @@
       </c>
       <c r="AI188" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -25593,7 +25593,7 @@
       </c>
       <c r="AI189" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -25726,7 +25726,7 @@
       </c>
       <c r="AI190" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -25859,7 +25859,7 @@
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -25992,7 +25992,7 @@
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -26125,7 +26125,7 @@
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -26258,7 +26258,7 @@
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="AI195" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -26524,7 +26524,7 @@
       </c>
       <c r="AI196" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -26657,7 +26657,7 @@
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -26790,7 +26790,7 @@
       </c>
       <c r="AI198" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -26923,7 +26923,7 @@
       </c>
       <c r="AI199" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -27056,7 +27056,7 @@
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -27189,7 +27189,7 @@
       </c>
       <c r="AI201" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -27322,7 +27322,7 @@
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -27455,7 +27455,7 @@
       </c>
       <c r="AI203" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -27588,7 +27588,7 @@
       </c>
       <c r="AI204" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -27721,7 +27721,7 @@
       </c>
       <c r="AI205" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -27854,7 +27854,7 @@
       </c>
       <c r="AI206" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -27987,7 +27987,7 @@
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -28120,7 +28120,7 @@
       </c>
       <c r="AI208" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -28253,7 +28253,7 @@
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -28386,7 +28386,7 @@
       </c>
       <c r="AI210" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -28519,7 +28519,7 @@
       </c>
       <c r="AI211" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -28652,7 +28652,7 @@
       </c>
       <c r="AI212" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -28785,7 +28785,7 @@
       </c>
       <c r="AI213" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -28918,7 +28918,7 @@
       </c>
       <c r="AI214" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -29051,7 +29051,7 @@
       </c>
       <c r="AI215" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -29184,7 +29184,7 @@
       </c>
       <c r="AI216" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -29317,7 +29317,7 @@
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -29450,7 +29450,7 @@
       </c>
       <c r="AI218" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -29583,7 +29583,7 @@
       </c>
       <c r="AI219" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -29716,7 +29716,7 @@
       </c>
       <c r="AI220" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -29849,7 +29849,7 @@
       </c>
       <c r="AI221" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -29982,7 +29982,7 @@
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -30115,7 +30115,7 @@
       </c>
       <c r="AI223" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -30248,7 +30248,7 @@
       </c>
       <c r="AI224" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -30381,7 +30381,7 @@
       </c>
       <c r="AI225" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -30514,7 +30514,7 @@
       </c>
       <c r="AI226" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -30647,7 +30647,7 @@
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -30780,7 +30780,7 @@
       </c>
       <c r="AI228" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -30913,7 +30913,7 @@
       </c>
       <c r="AI229" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -31046,7 +31046,7 @@
       </c>
       <c r="AI230" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -31179,7 +31179,7 @@
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -31312,7 +31312,7 @@
       </c>
       <c r="AI232" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -31445,7 +31445,7 @@
       </c>
       <c r="AI233" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -31578,7 +31578,7 @@
       </c>
       <c r="AI234" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -31711,7 +31711,7 @@
       </c>
       <c r="AI235" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -31844,7 +31844,7 @@
       </c>
       <c r="AI236" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -31977,7 +31977,7 @@
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -32110,7 +32110,7 @@
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -32243,7 +32243,7 @@
       </c>
       <c r="AI239" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -32376,7 +32376,7 @@
       </c>
       <c r="AI240" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -32509,7 +32509,7 @@
       </c>
       <c r="AI241" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -32642,7 +32642,7 @@
       </c>
       <c r="AI242" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -32775,7 +32775,7 @@
       </c>
       <c r="AI243" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -32908,7 +32908,7 @@
       </c>
       <c r="AI244" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -33041,7 +33041,7 @@
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -33174,7 +33174,7 @@
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -33307,7 +33307,7 @@
       </c>
       <c r="AI247" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -33440,7 +33440,7 @@
       </c>
       <c r="AI248" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -33573,7 +33573,7 @@
       </c>
       <c r="AI249" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -33706,7 +33706,7 @@
       </c>
       <c r="AI250" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -33839,7 +33839,7 @@
       </c>
       <c r="AI251" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -33972,7 +33972,7 @@
       </c>
       <c r="AI252" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -34105,7 +34105,7 @@
       </c>
       <c r="AI253" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -34238,7 +34238,7 @@
       </c>
       <c r="AI254" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="AI255" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -34504,7 +34504,7 @@
       </c>
       <c r="AI256" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="AI257" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -34770,7 +34770,7 @@
       </c>
       <c r="AI258" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -34903,7 +34903,7 @@
       </c>
       <c r="AI259" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -35036,7 +35036,7 @@
       </c>
       <c r="AI260" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -35169,7 +35169,7 @@
       </c>
       <c r="AI261" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -35302,7 +35302,7 @@
       </c>
       <c r="AI262" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -35435,7 +35435,7 @@
       </c>
       <c r="AI263" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -35568,7 +35568,7 @@
       </c>
       <c r="AI264" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -35701,7 +35701,7 @@
       </c>
       <c r="AI265" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -35834,7 +35834,7 @@
       </c>
       <c r="AI266" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -35967,7 +35967,7 @@
       </c>
       <c r="AI267" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -36100,7 +36100,7 @@
       </c>
       <c r="AI268" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -36233,7 +36233,7 @@
       </c>
       <c r="AI269" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -36366,7 +36366,7 @@
       </c>
       <c r="AI270" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -36499,7 +36499,7 @@
       </c>
       <c r="AI271" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="AI272" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -36765,7 +36765,7 @@
       </c>
       <c r="AI273" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -36898,7 +36898,7 @@
       </c>
       <c r="AI274" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -37031,7 +37031,7 @@
       </c>
       <c r="AI275" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -37164,7 +37164,7 @@
       </c>
       <c r="AI276" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -37297,7 +37297,7 @@
       </c>
       <c r="AI277" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -37430,7 +37430,7 @@
       </c>
       <c r="AI278" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -37563,7 +37563,7 @@
       </c>
       <c r="AI279" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -37696,7 +37696,7 @@
       </c>
       <c r="AI280" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -37829,7 +37829,7 @@
       </c>
       <c r="AI281" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -37962,7 +37962,7 @@
       </c>
       <c r="AI282" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -38095,7 +38095,7 @@
       </c>
       <c r="AI283" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -38228,7 +38228,7 @@
       </c>
       <c r="AI284" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -38361,7 +38361,7 @@
       </c>
       <c r="AI285" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -38494,7 +38494,7 @@
       </c>
       <c r="AI286" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -38627,7 +38627,7 @@
       </c>
       <c r="AI287" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -38760,7 +38760,7 @@
       </c>
       <c r="AI288" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -38893,7 +38893,7 @@
       </c>
       <c r="AI289" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -39006,7 +39006,7 @@
       </c>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2800 - Realizar Formação para Trabalhadores do Serviço CAPS Alc/Drogas II Pinheiros</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -39026,7 +39026,7 @@
       </c>
       <c r="AI290" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -39139,7 +39139,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E1240 - Implantação de um Centro de Exames da Mulher na região da Vila Prudente</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -39159,7 +39159,7 @@
       </c>
       <c r="AI291" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -39272,7 +39272,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Apoio às Atividades de Promoção da Cidadania Realizadas pela UNAS Heliópolis</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -39292,7 +39292,7 @@
       </c>
       <c r="AI292" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -39405,7 +39405,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Apoio às Atividades do Instituto Vladimir Herzog</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -39425,7 +39425,7 @@
       </c>
       <c r="AI293" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -39538,7 +39538,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Apoio ao Museu da Pessoa para Administração do Acervo do Professor Paul Singer</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="AI294" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -39671,7 +39671,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Apoio à Pesquisa sobre Renda Digna com a UNAS Heliópolis e Observatório De Olho Na Quebrada</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -39691,7 +39691,7 @@
       </c>
       <c r="AI295" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -39804,7 +39804,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Atendimentos e Formações para Familiares e Sobreviventes das Prisões pela Associação AMPARAR</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -39824,7 +39824,7 @@
       </c>
       <c r="AI296" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -39937,7 +39937,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Facilitar a Regularização Migratória e o Acesso aos Serviços Públicos para Migrantes por meio do CDH</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -39957,7 +39957,7 @@
       </c>
       <c r="AI297" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -40090,7 +40090,7 @@
       </c>
       <c r="AI298" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -40223,7 +40223,7 @@
       </c>
       <c r="AI299" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="AI300" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -40489,7 +40489,7 @@
       </c>
       <c r="AI301" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -40622,7 +40622,7 @@
       </c>
       <c r="AI302" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -40755,7 +40755,7 @@
       </c>
       <c r="AI303" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -40888,7 +40888,7 @@
       </c>
       <c r="AI304" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -41021,7 +41021,7 @@
       </c>
       <c r="AI305" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -41154,7 +41154,7 @@
       </c>
       <c r="AI306" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -41287,7 +41287,7 @@
       </c>
       <c r="AI307" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -41420,7 +41420,7 @@
       </c>
       <c r="AI308" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -41553,7 +41553,7 @@
       </c>
       <c r="AI309" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -41686,7 +41686,7 @@
       </c>
       <c r="AI310" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -41819,7 +41819,7 @@
       </c>
       <c r="AI311" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -41952,7 +41952,7 @@
       </c>
       <c r="AI312" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -42085,7 +42085,7 @@
       </c>
       <c r="AI313" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -42218,7 +42218,7 @@
       </c>
       <c r="AI314" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -42351,7 +42351,7 @@
       </c>
       <c r="AI315" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -42484,7 +42484,7 @@
       </c>
       <c r="AI316" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -42617,7 +42617,7 @@
       </c>
       <c r="AI317" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -42750,7 +42750,7 @@
       </c>
       <c r="AI318" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -42883,7 +42883,7 @@
       </c>
       <c r="AI319" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -43016,7 +43016,7 @@
       </c>
       <c r="AI320" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -43149,7 +43149,7 @@
       </c>
       <c r="AI321" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -43282,7 +43282,7 @@
       </c>
       <c r="AI322" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -43415,7 +43415,7 @@
       </c>
       <c r="AI323" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -43548,7 +43548,7 @@
       </c>
       <c r="AI324" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
       </c>
       <c r="AI325" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -43814,7 +43814,7 @@
       </c>
       <c r="AI326" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -43947,7 +43947,7 @@
       </c>
       <c r="AI327" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -44080,7 +44080,7 @@
       </c>
       <c r="AI328" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -44213,7 +44213,7 @@
       </c>
       <c r="AI329" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E3734 - Ampliação do Atendimento (24h) da Divisão da Fauna Silvestre (DFS) do Ibirapuera</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="AI330" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -44459,7 +44459,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2064 - Criação de Passeio Público Interno à Praça, Construção Escada de Acesso, Reforma e Adequação</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -44479,7 +44479,7 @@
       </c>
       <c r="AI331" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -44612,7 +44612,7 @@
       </c>
       <c r="AI332" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -44745,7 +44745,7 @@
       </c>
       <c r="AI333" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -44878,7 +44878,7 @@
       </c>
       <c r="AI334" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -45011,7 +45011,7 @@
       </c>
       <c r="AI335" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -45144,7 +45144,7 @@
       </c>
       <c r="AI336" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -45277,7 +45277,7 @@
       </c>
       <c r="AI337" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -45410,7 +45410,7 @@
       </c>
       <c r="AI338" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -45543,7 +45543,7 @@
       </c>
       <c r="AI339" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -45676,7 +45676,7 @@
       </c>
       <c r="AI340" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -45809,7 +45809,7 @@
       </c>
       <c r="AI341" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -45942,7 +45942,7 @@
       </c>
       <c r="AI342" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -46075,7 +46075,7 @@
       </c>
       <c r="AI343" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -46208,7 +46208,7 @@
       </c>
       <c r="AI344" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -46341,7 +46341,7 @@
       </c>
       <c r="AI345" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -46474,7 +46474,7 @@
       </c>
       <c r="AI346" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -46607,7 +46607,7 @@
       </c>
       <c r="AI347" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -46740,7 +46740,7 @@
       </c>
       <c r="AI348" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -46873,7 +46873,7 @@
       </c>
       <c r="AI349" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -47006,7 +47006,7 @@
       </c>
       <c r="AI350" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -47139,7 +47139,7 @@
       </c>
       <c r="AI351" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -47272,7 +47272,7 @@
       </c>
       <c r="AI352" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -47405,7 +47405,7 @@
       </c>
       <c r="AI353" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -47538,7 +47538,7 @@
       </c>
       <c r="AI354" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -47671,7 +47671,7 @@
       </c>
       <c r="AI355" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -47804,7 +47804,7 @@
       </c>
       <c r="AI356" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -47937,7 +47937,7 @@
       </c>
       <c r="AI357" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -48070,7 +48070,7 @@
       </c>
       <c r="AI358" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -48203,7 +48203,7 @@
       </c>
       <c r="AI359" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -48336,7 +48336,7 @@
       </c>
       <c r="AI360" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -48469,7 +48469,7 @@
       </c>
       <c r="AI361" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -48602,7 +48602,7 @@
       </c>
       <c r="AI362" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -48735,7 +48735,7 @@
       </c>
       <c r="AI363" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -48868,7 +48868,7 @@
       </c>
       <c r="AI364" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -49001,7 +49001,7 @@
       </c>
       <c r="AI365" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -49134,7 +49134,7 @@
       </c>
       <c r="AI366" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -49267,7 +49267,7 @@
       </c>
       <c r="AI367" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -49400,7 +49400,7 @@
       </c>
       <c r="AI368" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -49533,7 +49533,7 @@
       </c>
       <c r="AI369" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -49666,7 +49666,7 @@
       </c>
       <c r="AI370" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -49799,7 +49799,7 @@
       </c>
       <c r="AI371" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -49932,7 +49932,7 @@
       </c>
       <c r="AI372" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -50065,7 +50065,7 @@
       </c>
       <c r="AI373" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -50198,7 +50198,7 @@
       </c>
       <c r="AI374" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -50331,7 +50331,7 @@
       </c>
       <c r="AI375" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -50464,7 +50464,7 @@
       </c>
       <c r="AI376" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
@@ -50597,7 +50597,7 @@
       </c>
       <c r="AI377" t="inlineStr">
         <is>
-          <t>02/03/2026 15:29:31</t>
+          <t>03/03/2026 12:22:05</t>
         </is>
       </c>
     </row>
